--- a/reports/tables/comparativa_final_diabetes.xlsx
+++ b/reports/tables/comparativa_final_diabetes.xlsx
@@ -521,22 +521,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7202</v>
+        <v>0.7147</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.7531</v>
+        <v>0.7556</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.0692</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2203</v>
+        <v>0.217</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.3409</v>
+        <v>0.3372</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>0.8066</v>
+        <v>0.8055</v>
       </c>
     </row>
     <row r="4">
@@ -571,22 +571,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5884</v>
+        <v>0.5163</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>0.8903</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0.1097</v>
+        <v>0.9352</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0.0611</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.1758</v>
+        <v>0.1584</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.2936</v>
+        <v>0.2709</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.7958</v>
+        <v>0.7922</v>
       </c>
     </row>
   </sheetData>
